--- a/samples/clover/design-data/xlsx/Shop.xlsx
+++ b/samples/clover/design-data/xlsx/Shop.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[ShopSlotWeight!$B$2:$D$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[BoosterPack!$B$2:$G$19]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Voucher!$B$2:$F$36]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[VoucherEffect!$B$2:$BL$38]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[VoucherEffect!$B$2:$BM$38]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[RerollCost!$B$2:$C$14]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="263">
   <si>
     <t xml:space="preserve">:table ShopSlotWeight(key=item)</t>
   </si>
@@ -650,6 +650,9 @@
   </si>
   <si>
     <t xml:space="preserve">operation.handler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operation.sticker</t>
   </si>
   <si>
     <t xml:space="preserve">foreign Voucher</t>
@@ -2168,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL38"/>
+  <dimension ref="A1:BM38"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.046875" customWidth="1"/>
@@ -2220,7 +2223,7 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2292,6 +2295,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -2486,43 +2490,46 @@
       <c r="BL2" s="4" t="s">
         <v>208</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -2539,7 +2546,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -2578,43 +2585,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -2631,7 +2639,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -2670,6 +2678,7 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -2679,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>81</v>
@@ -2697,22 +2706,22 @@
         <v>81</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH5" s="5">
         <v>1</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
@@ -2723,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>81</v>
@@ -2741,22 +2750,22 @@
         <v>81</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH6" s="6">
         <v>1</v>
       </c>
       <c r="BF6" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
@@ -2767,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>81</v>
@@ -2785,25 +2794,25 @@
         <v>81</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH7" s="5">
         <v>25</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BG7" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>81</v>
@@ -2832,25 +2841,25 @@
         <v>81</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH8" s="6">
         <v>50</v>
       </c>
       <c r="BF8" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BG8" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9">
@@ -2861,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>81</v>
@@ -2879,25 +2888,25 @@
         <v>81</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH9" s="5">
         <v>2</v>
       </c>
       <c r="BF9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="BG9" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="BG9" s="5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2908,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>81</v>
@@ -2926,25 +2935,25 @@
         <v>81</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH10" s="6">
         <v>4</v>
       </c>
       <c r="BF10" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="BG10" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="BG10" s="6" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -2955,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>81</v>
@@ -2973,22 +2982,22 @@
         <v>81</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH11" s="5">
         <v>-2</v>
       </c>
       <c r="BF11" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -2999,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>81</v>
@@ -3017,22 +3026,22 @@
         <v>81</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH12" s="6">
         <v>-2</v>
       </c>
       <c r="BF12" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -3043,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>81</v>
@@ -3061,22 +3070,22 @@
         <v>81</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH13" s="5">
         <v>1</v>
       </c>
       <c r="BF13" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
@@ -3087,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>81</v>
@@ -3105,22 +3114,22 @@
         <v>81</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH14" s="6">
         <v>1</v>
       </c>
       <c r="BF14" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
@@ -3131,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>81</v>
@@ -3149,22 +3158,22 @@
         <v>81</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH15" s="5">
         <v>1</v>
       </c>
       <c r="BF15" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
@@ -3175,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>81</v>
@@ -3193,25 +3202,25 @@
         <v>81</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH16" s="6">
         <v>15000</v>
       </c>
       <c r="BF16" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BG16" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17">
@@ -3222,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>81</v>
@@ -3240,22 +3249,22 @@
         <v>81</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH17" s="5">
         <v>1</v>
       </c>
       <c r="BF17" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18">
@@ -3266,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -3284,22 +3293,22 @@
         <v>81</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH18" s="6">
         <v>1</v>
       </c>
       <c r="BF18" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19">
@@ -3310,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>81</v>
@@ -3328,22 +3337,22 @@
         <v>81</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
       </c>
       <c r="BF19" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
@@ -3354,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -3372,22 +3381,22 @@
         <v>81</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
       </c>
       <c r="BF20" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
@@ -3398,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>81</v>
@@ -3416,25 +3425,25 @@
         <v>81</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH21" s="5">
         <v>2</v>
       </c>
       <c r="BF21" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="BG21" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22">
@@ -3445,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>81</v>
@@ -3463,25 +3472,25 @@
         <v>81</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH22" s="6">
         <v>4</v>
       </c>
       <c r="BF22" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="BG22" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23">
@@ -3492,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>81</v>
@@ -3510,25 +3519,25 @@
         <v>81</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH23" s="5">
         <v>2</v>
       </c>
       <c r="BF23" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="BG23" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24">
@@ -3539,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>81</v>
@@ -3557,25 +3566,25 @@
         <v>81</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH24" s="6">
         <v>4</v>
       </c>
       <c r="BF24" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="BG24" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25">
@@ -3586,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>81</v>
@@ -3604,25 +3613,25 @@
         <v>81</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH25" s="5">
         <v>10</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BG25" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26">
@@ -3633,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>81</v>
@@ -3651,25 +3660,25 @@
         <v>81</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH26" s="6">
         <v>20</v>
       </c>
       <c r="BF26" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BG26" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
@@ -3680,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>81</v>
@@ -3698,16 +3707,16 @@
         <v>81</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
@@ -3718,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>81</v>
@@ -3736,22 +3745,22 @@
         <v>81</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH28" s="6">
         <v>1</v>
       </c>
       <c r="BF28" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29">
@@ -3762,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>81</v>
@@ -3780,22 +3789,22 @@
         <v>81</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA29" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH29" s="5">
         <v>1</v>
       </c>
       <c r="BF29" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30">
@@ -3806,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>81</v>
@@ -3824,22 +3833,22 @@
         <v>81</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA30" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH30" s="6">
         <v>1</v>
       </c>
       <c r="BF30" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31">
@@ -3850,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>81</v>
@@ -3868,22 +3877,22 @@
         <v>81</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA31" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH31" s="5">
         <v>-1</v>
       </c>
       <c r="BF31" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32">
@@ -3894,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>81</v>
@@ -3912,22 +3921,22 @@
         <v>81</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA32" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH32" s="6">
         <v>-1</v>
       </c>
       <c r="BF32" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33">
@@ -3938,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>81</v>
@@ -3956,22 +3965,22 @@
         <v>81</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA33" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH33" s="5">
         <v>-1</v>
       </c>
       <c r="BF33" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34">
@@ -3982,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>81</v>
@@ -4000,22 +4009,22 @@
         <v>81</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH34" s="6">
         <v>-1</v>
       </c>
       <c r="BF34" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35">
@@ -4026,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>81</v>
@@ -4044,25 +4053,25 @@
         <v>81</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K35" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA35" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH35" s="5">
         <v>1</v>
       </c>
       <c r="BF35" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BG35" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36">
@@ -4073,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>81</v>
@@ -4091,25 +4100,25 @@
         <v>81</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA36" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH36" s="6">
         <v>99</v>
       </c>
       <c r="BF36" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BG36" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37">
@@ -4120,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>81</v>
@@ -4138,22 +4147,22 @@
         <v>81</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>81</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA37" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH37" s="5">
         <v>1</v>
       </c>
       <c r="BF37" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38">
@@ -4164,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>81</v>
@@ -4182,26 +4191,26 @@
         <v>81</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA38" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH38" s="6">
         <v>1</v>
       </c>
       <c r="BF38" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL38"/>
+  <autoFilter ref="B2:BM38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4218,10 +4227,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -4230,7 +4239,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>29</v>
@@ -4241,7 +4250,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
@@ -4252,10 +4261,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
